--- a/ig/ch-elm/StructureDefinition-ch-elm-specimen.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-specimen.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2110" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2110" uniqueCount="404">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -716,7 +716,7 @@
     <t>Specimen.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -777,7 +777,7 @@
     <t>bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite}
+    <t xml:space="preserve">Extension {bodySite|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -785,18 +785,18 @@
   </si>
   <si>
     <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
-  </si>
-  <si>
-    <t>Specimen.collection.extension:bodySite.id</t>
-  </si>
-  <si>
-    <t>Specimen.collection.extension.id</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
+    <t>Specimen.collection.extension:bodySite.id</t>
+  </si>
+  <si>
+    <t>Specimen.collection.extension.id</t>
+  </si>
+  <si>
     <t>Specimen.collection.extension:bodySite.extension</t>
   </si>
   <si>
@@ -837,14 +837,10 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
   </si>
   <si>
     <t>Specimen.collection.modifierExtension</t>
@@ -867,7 +863,7 @@
     <t>Specimen.collection.collector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -938,7 +934,7 @@
     <t>Specimen.collection.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -969,7 +965,7 @@
     <t>The  technique that is used to perform the procedure.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-collection-method</t>
+    <t>http://hl7.org/fhir/ValueSet/specimen-collection-method|4.0.1</t>
   </si>
   <si>
     <t>.methodCode</t>
@@ -1024,7 +1020,7 @@
     <t>Codes describing the fasting status of the patient.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0916</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0916|2.9</t>
   </si>
   <si>
     <t>OBR-</t>
@@ -1075,7 +1071,7 @@
     <t>Type indicating the technique used to process the specimen.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure</t>
+    <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure|4.0.1</t>
   </si>
   <si>
     <t>Specimen.processing.additive</t>
@@ -1216,7 +1212,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Substance)</t>
+Reference(Substance|4.0.1)</t>
   </si>
   <si>
     <t>Additive associated with container</t>
@@ -1228,7 +1224,7 @@
     <t>Substance added to specimen container.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0371</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0371|2.9</t>
   </si>
   <si>
     <t>.scopesRole[classCode=ADTV].player</t>
@@ -1255,7 +1251,7 @@
     <t>Codes describing the state of the specimen.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0493</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0493|2.9</t>
   </si>
   <si>
     <t>SPM-24</t>
@@ -4497,7 +4493,7 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>137</v>
@@ -4514,10 +4510,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4540,7 +4536,7 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>176</v>
@@ -4606,7 +4602,7 @@
         <v>86</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>249</v>
+        <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>77</v>
@@ -4935,7 +4931,7 @@
         <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>265</v>
+        <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>98</v>
@@ -4952,14 +4948,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4981,10 +4977,10 @@
         <v>132</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>135</v>
@@ -5039,7 +5035,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5065,10 +5061,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5091,13 +5087,13 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5148,7 +5144,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5163,21 +5159,21 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>277</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5200,13 +5196,13 @@
         <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5245,7 +5241,7 @@
         <v>77</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -5255,7 +5251,7 @@
         <v>184</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5270,24 +5266,24 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>285</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="C34" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>77</v>
@@ -5312,10 +5308,10 @@
         <v>212</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5366,7 +5362,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5378,24 +5374,24 @@
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>285</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5418,13 +5414,13 @@
         <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5475,7 +5471,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5493,7 +5489,7 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5501,10 +5497,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5527,13 +5523,13 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5584,7 +5580,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5599,21 +5595,21 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>298</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5639,10 +5635,10 @@
         <v>166</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5669,14 +5665,14 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="Y37" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="Y37" t="s" s="2">
+      <c r="Z37" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>304</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
       </c>
@@ -5693,7 +5689,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5708,21 +5704,21 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5748,13 +5744,13 @@
         <v>166</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5784,7 +5780,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -5802,7 +5798,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5817,21 +5813,21 @@
         <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5854,19 +5850,19 @@
         <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5891,14 +5887,14 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="Y39" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="Y39" t="s" s="2">
+      <c r="Z39" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>322</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
       </c>
@@ -5915,7 +5911,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5936,15 +5932,15 @@
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5970,10 +5966,10 @@
         <v>233</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6024,7 +6020,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6039,7 +6035,7 @@
         <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>77</v>
@@ -6050,10 +6046,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6159,10 +6155,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6270,14 +6266,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6299,10 +6295,10 @@
         <v>132</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>135</v>
@@ -6357,7 +6353,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6383,10 +6379,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6412,10 +6408,10 @@
         <v>175</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6466,7 +6462,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6481,7 +6477,7 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>77</v>
@@ -6492,10 +6488,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6521,10 +6517,10 @@
         <v>166</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6551,14 +6547,14 @@
         <v>77</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>339</v>
-      </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
       </c>
@@ -6575,7 +6571,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6601,10 +6597,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6627,13 +6623,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6684,7 +6680,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6699,21 +6695,21 @@
         <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>345</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6736,13 +6732,13 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6793,7 +6789,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6808,7 +6804,7 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>77</v>
@@ -6819,10 +6815,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6848,10 +6844,10 @@
         <v>233</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6902,7 +6898,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6917,7 +6913,7 @@
         <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>77</v>
@@ -6928,10 +6924,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7037,10 +7033,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7144,13 +7140,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>77</v>
@@ -7172,13 +7168,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7238,7 +7234,7 @@
         <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>137</v>
@@ -7255,14 +7251,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7284,10 +7280,10 @@
         <v>132</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>135</v>
@@ -7342,7 +7338,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7368,10 +7364,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7397,10 +7393,10 @@
         <v>144</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7451,7 +7447,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7472,15 +7468,15 @@
         <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7506,10 +7502,10 @@
         <v>175</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7560,7 +7556,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7575,7 +7571,7 @@
         <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>77</v>
@@ -7586,10 +7582,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7615,10 +7611,10 @@
         <v>166</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7649,7 +7645,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -7667,7 +7663,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7688,15 +7684,15 @@
         <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7719,13 +7715,13 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7776,7 +7772,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7791,21 +7787,21 @@
         <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>378</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7828,13 +7824,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7885,7 +7881,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -7900,21 +7896,21 @@
         <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>383</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7937,13 +7933,13 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7970,14 +7966,14 @@
         <v>77</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>389</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
       </c>
@@ -7994,7 +7990,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8009,21 +8005,21 @@
         <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>391</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8049,16 +8045,16 @@
         <v>166</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8083,14 +8079,14 @@
         <v>77</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>398</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>77</v>
       </c>
@@ -8107,7 +8103,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8128,15 +8124,15 @@
         <v>77</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8159,13 +8155,13 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L60" t="s" s="2">
         <v>51</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8216,7 +8212,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8231,13 +8227,13 @@
         <v>98</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>404</v>
       </c>
     </row>
   </sheetData>

--- a/ig/ch-elm/StructureDefinition-ch-elm-specimen.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-specimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1020,7 +1020,7 @@
     <t>Codes describing the fasting status of the patient.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0916|2.9</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0916|3.0.0</t>
   </si>
   <si>
     <t>OBR-</t>
@@ -1224,7 +1224,7 @@
     <t>Substance added to specimen container.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0371|2.9</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0371|3.0.0</t>
   </si>
   <si>
     <t>.scopesRole[classCode=ADTV].player</t>
@@ -1251,7 +1251,7 @@
     <t>Codes describing the state of the specimen.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0493|2.9</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0493|3.0.0</t>
   </si>
   <si>
     <t>SPM-24</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-specimen.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-specimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-specimen.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-specimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
